--- a/Denner/Import-nationale-Artikel-DPB/Import 2/Artikelstammdaten_PLU_Andere_WG_v01.xlsx
+++ b/Denner/Import-nationale-Artikel-DPB/Import 2/Artikelstammdaten_PLU_Andere_WG_v01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://advellencesolutionsag-my.sharepoint.com/personal/otto_mischler_advellence_com/Documents/Dokumente/Projekte/Denner/1629-Regio-Artikel/Import-nationale-Artikel-DPB/Import 2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Projeke\Denner\Import-nationale-Artikel-DPB\Import 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3769" documentId="8_{B7BF4E50-0F3B-4055-B31C-2020BB68A1D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63F44251-FB5E-464A-9433-7ED8E7D5EBA0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C630AC3-097C-453A-9C3A-011C89FCAD64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-12780" yWindow="-17388" windowWidth="30936" windowHeight="16776" firstSheet="1" activeTab="1" xr2:uid="{98473891-E57A-40FB-AED9-CDCC45FC270D}"/>
+    <workbookView xWindow="-5510" yWindow="-21710" windowWidth="38620" windowHeight="21100" firstSheet="1" activeTab="1" xr2:uid="{98473891-E57A-40FB-AED9-CDCC45FC270D}"/>
   </bookViews>
   <sheets>
     <sheet name="Abkürzungen_WG" sheetId="17" r:id="rId1"/>
@@ -6813,6 +6813,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A855C53-24C0-4D6A-B3F7-850D03E51587}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AJ208"/>
   <sheetFormatPr defaultColWidth="11.46484375" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
@@ -6963,7 +6964,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -7071,7 +7072,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -7179,7 +7180,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -7287,7 +7288,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -7395,7 +7396,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -7503,7 +7504,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -7611,7 +7612,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -7719,7 +7720,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -7821,7 +7822,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -7923,7 +7924,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -8031,7 +8032,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -8139,7 +8140,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -8247,7 +8248,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -8355,7 +8356,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -8463,7 +8464,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -8571,7 +8572,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -8679,7 +8680,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -8787,7 +8788,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
         <v>22</v>
       </c>
@@ -8895,7 +8896,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
         <v>23</v>
       </c>
@@ -9003,7 +9004,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
         <v>24</v>
       </c>
@@ -9111,7 +9112,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4">
         <v>25</v>
       </c>
@@ -9219,7 +9220,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4">
         <v>26</v>
       </c>
@@ -9327,7 +9328,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4">
         <v>27</v>
       </c>
@@ -9435,7 +9436,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4">
         <v>28</v>
       </c>
@@ -9543,7 +9544,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4">
         <v>29</v>
       </c>
@@ -9651,7 +9652,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4">
         <v>30</v>
       </c>
@@ -9759,7 +9760,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="4">
         <v>31</v>
       </c>
@@ -9867,7 +9868,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4">
         <v>33</v>
       </c>
@@ -9975,7 +9976,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="4">
         <v>35</v>
       </c>
@@ -10083,7 +10084,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="4">
         <v>36</v>
       </c>
@@ -10191,7 +10192,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4">
         <v>37</v>
       </c>
@@ -10299,7 +10300,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="33" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="4">
         <v>39</v>
       </c>
@@ -10407,7 +10408,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="34" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="4">
         <v>40</v>
       </c>
@@ -10515,7 +10516,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="35" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="4">
         <v>41</v>
       </c>
@@ -10623,7 +10624,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="36" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="4">
         <v>43</v>
       </c>
@@ -10731,7 +10732,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="37" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="4">
         <v>44</v>
       </c>
@@ -10839,7 +10840,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="38" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="4">
         <v>45</v>
       </c>
@@ -10947,7 +10948,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="39" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="4">
         <v>46</v>
       </c>
@@ -11055,7 +11056,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="40" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="4">
         <v>47</v>
       </c>
@@ -11163,7 +11164,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="41" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="4">
         <v>48</v>
       </c>
@@ -11271,7 +11272,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="42" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="4">
         <v>49</v>
       </c>
@@ -11379,7 +11380,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="43" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4">
         <v>50</v>
       </c>
@@ -11487,7 +11488,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="44" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="4">
         <v>51</v>
       </c>
@@ -11595,7 +11596,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="45" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4">
         <v>52</v>
       </c>
@@ -11703,7 +11704,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="4">
         <v>53</v>
       </c>
@@ -11811,7 +11812,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="47" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="4">
         <v>54</v>
       </c>
@@ -11919,7 +11920,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="48" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="4">
         <v>55</v>
       </c>
@@ -12027,7 +12028,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="49" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="4">
         <v>18</v>
       </c>
@@ -12135,7 +12136,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="50" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="4">
         <v>34</v>
       </c>
@@ -12243,7 +12244,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="51" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="4">
         <v>38</v>
       </c>
@@ -12351,7 +12352,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="52" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="4">
         <v>38</v>
       </c>
@@ -12459,7 +12460,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="53" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="4">
         <v>19</v>
       </c>
@@ -12567,7 +12568,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="54" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="4">
         <v>19</v>
       </c>
@@ -12675,7 +12676,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="4">
         <v>20</v>
       </c>
@@ -12783,7 +12784,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="56" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="4">
         <v>21</v>
       </c>
@@ -12891,7 +12892,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="57" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="4">
         <v>21</v>
       </c>
@@ -12999,7 +13000,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="4">
         <v>62</v>
       </c>
@@ -13107,7 +13108,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="4">
         <v>62</v>
       </c>
@@ -13215,7 +13216,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="60" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="4">
         <v>64</v>
       </c>
@@ -13323,7 +13324,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="61" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="4">
         <v>64</v>
       </c>
@@ -13431,7 +13432,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="62" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="4">
         <v>63</v>
       </c>
@@ -13539,7 +13540,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="63" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="4">
         <v>56</v>
       </c>
@@ -13647,7 +13648,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="64" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="4">
         <v>56</v>
       </c>
@@ -13755,7 +13756,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="65" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="4">
         <v>57</v>
       </c>
@@ -13863,7 +13864,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" s="4">
         <v>58</v>
       </c>
@@ -13971,7 +13972,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="67" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="4">
         <v>59</v>
       </c>
@@ -14079,7 +14080,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="68" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="4">
         <v>61</v>
       </c>
@@ -14187,7 +14188,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="69" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" s="4">
         <v>61</v>
       </c>
@@ -14295,7 +14296,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="70" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="4">
         <v>61</v>
       </c>
@@ -14403,7 +14404,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="71" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" s="4">
         <v>61</v>
       </c>
@@ -14511,7 +14512,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="72" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" s="4">
         <v>60</v>
       </c>
@@ -14619,7 +14620,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="73" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="4">
         <v>74</v>
       </c>
@@ -14727,7 +14728,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="74" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" s="4">
         <v>75</v>
       </c>
@@ -14835,7 +14836,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="75" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" s="4">
         <v>76</v>
       </c>
@@ -14943,7 +14944,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="76" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" s="4">
         <v>77</v>
       </c>
@@ -15051,7 +15052,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="77" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="4">
         <v>94</v>
       </c>
@@ -15159,7 +15160,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="78" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="4">
         <v>95</v>
       </c>
@@ -15267,7 +15268,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="79" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="4">
         <v>100</v>
       </c>
@@ -15375,7 +15376,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="80" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="4">
         <v>100</v>
       </c>
@@ -15483,7 +15484,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="81" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="4">
         <v>100</v>
       </c>
@@ -15591,7 +15592,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="82" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" s="4">
         <v>73</v>
       </c>
@@ -15699,7 +15700,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="83" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="4">
         <v>98</v>
       </c>
@@ -15807,7 +15808,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="84" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="4">
         <v>99</v>
       </c>
@@ -15915,7 +15916,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="85" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="4">
         <v>99</v>
       </c>
@@ -16023,7 +16024,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="86" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" s="4">
         <v>101</v>
       </c>
@@ -16131,7 +16132,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="87" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="4">
         <v>101</v>
       </c>
@@ -16239,7 +16240,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="88" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" s="4">
         <v>66</v>
       </c>
@@ -16347,7 +16348,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="89" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="4">
         <v>79</v>
       </c>
@@ -16455,7 +16456,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="90" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="4">
         <v>80</v>
       </c>
@@ -16563,7 +16564,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="91" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="4">
         <v>81</v>
       </c>
@@ -16671,7 +16672,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="92" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" s="4">
         <v>82</v>
       </c>
@@ -16779,7 +16780,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="93" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" s="4">
         <v>83</v>
       </c>
@@ -16887,7 +16888,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="94" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" s="4">
         <v>87</v>
       </c>
@@ -16995,7 +16996,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="95" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="4">
         <v>87</v>
       </c>
@@ -17103,7 +17104,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="96" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" s="4">
         <v>88</v>
       </c>
@@ -17211,7 +17212,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="97" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" s="4">
         <v>88</v>
       </c>
@@ -17319,7 +17320,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="98" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" s="4">
         <v>93</v>
       </c>
@@ -17427,7 +17428,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="99" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" s="4">
         <v>96</v>
       </c>
@@ -17535,7 +17536,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="100" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" s="4">
         <v>102</v>
       </c>
@@ -17643,7 +17644,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="101" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" s="4">
         <v>67</v>
       </c>
@@ -17751,7 +17752,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="102" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="4">
         <v>68</v>
       </c>
@@ -17859,7 +17860,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="103" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="4">
         <v>69</v>
       </c>
@@ -17967,7 +17968,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="104" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="4">
         <v>71</v>
       </c>
@@ -18075,7 +18076,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="105" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="4">
         <v>72</v>
       </c>
@@ -18183,7 +18184,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="106" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="4">
         <v>85</v>
       </c>
@@ -18291,7 +18292,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="107" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="4">
         <v>85</v>
       </c>
@@ -18399,7 +18400,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="108" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="4">
         <v>85</v>
       </c>
@@ -18507,7 +18508,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="109" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" s="4">
         <v>85</v>
       </c>
@@ -18615,7 +18616,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="110" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" s="4">
         <v>85</v>
       </c>
@@ -18723,7 +18724,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="111" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" s="4">
         <v>86</v>
       </c>
@@ -18831,7 +18832,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="112" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="4">
         <v>86</v>
       </c>
@@ -18939,7 +18940,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="113" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" s="4">
         <v>89</v>
       </c>
@@ -19047,7 +19048,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="114" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" s="4">
         <v>89</v>
       </c>
@@ -19155,7 +19156,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="115" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" s="4">
         <v>89</v>
       </c>
@@ -19263,7 +19264,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="116" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" s="4">
         <v>92</v>
       </c>
@@ -19371,7 +19372,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="117" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" s="4">
         <v>78</v>
       </c>
@@ -19479,7 +19480,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="118" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" s="4">
         <v>78</v>
       </c>
@@ -19587,7 +19588,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="119" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" s="4">
         <v>65</v>
       </c>
@@ -19695,7 +19696,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="120" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" s="4">
         <v>70</v>
       </c>
@@ -19803,7 +19804,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="121" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" s="4">
         <v>84</v>
       </c>
@@ -19911,7 +19912,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="122" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" s="4">
         <v>90</v>
       </c>
@@ -20019,7 +20020,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="123" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" s="4">
         <v>91</v>
       </c>
@@ -20127,7 +20128,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="124" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" s="4">
         <v>97</v>
       </c>
@@ -20235,7 +20236,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="125" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" s="4">
         <v>109</v>
       </c>
@@ -20344,7 +20345,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="126" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" s="4">
         <v>109</v>
       </c>
@@ -20453,7 +20454,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="127" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" s="4">
         <v>109</v>
       </c>
@@ -20561,7 +20562,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="128" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" s="4">
         <v>108</v>
       </c>
@@ -20670,7 +20671,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="129" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" s="4">
         <v>108</v>
       </c>
@@ -20779,7 +20780,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="130" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" s="4">
         <v>108</v>
       </c>
@@ -20888,7 +20889,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="131" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" s="4">
         <v>108</v>
       </c>
@@ -20997,7 +20998,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="132" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" s="4">
         <v>108</v>
       </c>
@@ -21105,7 +21106,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="133" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" s="4">
         <v>109</v>
       </c>
@@ -21214,7 +21215,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="134" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" s="4">
         <v>109</v>
       </c>
@@ -21323,7 +21324,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="135" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" s="4">
         <v>109</v>
       </c>
@@ -21431,7 +21432,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="136" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" s="4">
         <v>109</v>
       </c>
@@ -21539,7 +21540,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="137" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" s="4">
         <v>114</v>
       </c>
@@ -21647,7 +21648,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="138" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" s="4">
         <v>114</v>
       </c>
@@ -21755,7 +21756,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="139" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" s="4">
         <v>114</v>
       </c>
@@ -21863,7 +21864,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="140" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" s="4">
         <v>115</v>
       </c>
@@ -21971,7 +21972,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="141" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" s="4">
         <v>115</v>
       </c>
@@ -22079,7 +22080,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="142" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" s="4">
         <v>115</v>
       </c>
@@ -22187,7 +22188,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="143" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" s="4">
         <v>103</v>
       </c>
@@ -22295,7 +22296,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="144" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" s="4">
         <v>104</v>
       </c>
@@ -22403,7 +22404,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="145" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" s="4">
         <v>111</v>
       </c>
@@ -22511,7 +22512,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="146" spans="1:36" s="33" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:36" s="33" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" s="4">
         <v>112</v>
       </c>
@@ -22619,7 +22620,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="147" spans="1:36" s="33" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:36" s="33" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" s="4">
         <v>113</v>
       </c>
@@ -22727,7 +22728,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="148" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" s="4">
         <v>117</v>
       </c>
@@ -22835,7 +22836,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="149" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" s="4">
         <v>118</v>
       </c>
@@ -22943,7 +22944,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="150" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" s="4">
         <v>119</v>
       </c>
@@ -23051,7 +23052,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="151" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" s="4">
         <v>120</v>
       </c>
@@ -23159,7 +23160,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="152" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" s="4">
         <v>105</v>
       </c>
@@ -23267,7 +23268,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="153" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" s="4">
         <v>105</v>
       </c>
@@ -23375,7 +23376,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="154" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" s="4">
         <v>105</v>
       </c>
@@ -23483,7 +23484,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="155" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" s="4">
         <v>105</v>
       </c>
@@ -23591,7 +23592,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="156" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" s="4">
         <v>106</v>
       </c>
@@ -23699,7 +23700,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="157" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" s="4">
         <v>107</v>
       </c>
@@ -23807,7 +23808,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="158" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" s="4">
         <v>107</v>
       </c>
@@ -23915,7 +23916,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="159" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" s="4">
         <v>122</v>
       </c>
@@ -24023,7 +24024,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="160" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" s="4">
         <v>122</v>
       </c>
@@ -24131,7 +24132,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="161" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" s="4">
         <v>122</v>
       </c>
@@ -24239,7 +24240,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="162" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" s="4">
         <v>122</v>
       </c>
@@ -24347,7 +24348,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="163" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" s="4">
         <v>105</v>
       </c>
@@ -24455,7 +24456,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="164" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" s="4">
         <v>105</v>
       </c>
@@ -24563,7 +24564,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="165" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" s="4">
         <v>105</v>
       </c>
@@ -24671,7 +24672,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="166" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" s="4">
         <v>105</v>
       </c>
@@ -24779,7 +24780,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="167" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" s="4">
         <v>105</v>
       </c>
@@ -24887,7 +24888,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="168" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" s="4">
         <v>121</v>
       </c>
@@ -24995,7 +24996,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="169" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" s="4">
         <v>121</v>
       </c>
@@ -25103,7 +25104,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="170" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" s="4">
         <v>121</v>
       </c>
@@ -25211,7 +25212,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="171" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" s="4">
         <v>121</v>
       </c>
@@ -25319,7 +25320,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="172" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" s="4">
         <v>121</v>
       </c>
@@ -25427,7 +25428,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="173" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" s="4">
         <v>121</v>
       </c>
@@ -25535,7 +25536,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="174" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" s="4">
         <v>121</v>
       </c>
@@ -25643,7 +25644,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="175" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" s="4">
         <v>121</v>
       </c>
@@ -25751,7 +25752,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="176" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" s="4">
         <v>123</v>
       </c>
@@ -25859,7 +25860,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="177" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" s="4">
         <v>123</v>
       </c>
@@ -25967,7 +25968,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="178" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" s="4">
         <v>129</v>
       </c>
@@ -26075,7 +26076,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="179" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" s="4">
         <v>130</v>
       </c>
@@ -26183,7 +26184,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="180" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" s="4">
         <v>131</v>
       </c>
@@ -26291,7 +26292,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="181" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" s="4">
         <v>132</v>
       </c>
@@ -26399,7 +26400,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="182" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" s="4">
         <v>133</v>
       </c>
@@ -26507,7 +26508,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="183" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" s="4">
         <v>129</v>
       </c>
@@ -26615,7 +26616,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="184" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" s="4">
         <v>130</v>
       </c>
@@ -26723,7 +26724,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="185" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" s="4">
         <v>131</v>
       </c>
@@ -26831,7 +26832,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="186" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" s="4">
         <v>132</v>
       </c>
@@ -26939,7 +26940,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="187" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" s="4">
         <v>133</v>
       </c>
@@ -27047,7 +27048,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="188" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" s="4">
         <v>139</v>
       </c>
@@ -27149,7 +27150,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="189" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" s="4">
         <v>140</v>
       </c>
@@ -27251,7 +27252,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="190" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" s="4">
         <v>141</v>
       </c>
@@ -27353,7 +27354,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="191" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" s="4">
         <v>142</v>
       </c>
@@ -27455,7 +27456,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="192" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" s="4">
         <v>144</v>
       </c>
@@ -28679,7 +28680,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="204" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" s="4">
         <v>146</v>
       </c>
@@ -28883,7 +28884,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="206" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" s="4">
         <v>147</v>
       </c>
@@ -28991,7 +28992,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="207" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" s="4">
         <v>147</v>
       </c>
@@ -29099,7 +29100,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="208" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:36" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" s="4">
         <v>147</v>
       </c>
@@ -29208,7 +29209,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ208" xr:uid="{4A855C53-24C0-4D6A-B3F7-850D03E51587}"/>
+  <autoFilter ref="A1:AJ208" xr:uid="{4A855C53-24C0-4D6A-B3F7-850D03E51587}">
+    <filterColumn colId="24">
+      <filters>
+        <filter val="0 - Ohne MWST"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AJ4">
     <sortCondition ref="A2:A4"/>
   </sortState>
@@ -59704,27 +59711,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Datum xmlns="b5dd9254-6a80-4550-b647-acdc8f5cf066" xsi:nil="true"/>
-    <TaxCatchAll xmlns="c58b33ff-7e07-4eb2-a566-ce2576b11ca3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1a3513a1-f8f9-433c-9b2a-5ef469d764af">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D97ACE3CC169BD409B2324F3F0D64773" ma:contentTypeVersion="9" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="a406959f5aa5704f71f31d25ca6cc23d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5dd9254-6a80-4550-b647-acdc8f5cf066" xmlns:ns3="9f573000-1803-4063-935f-650b3da64931" xmlns:ns4="1a3513a1-f8f9-433c-9b2a-5ef469d764af" xmlns:ns5="c58b33ff-7e07-4eb2-a566-ce2576b11ca3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1a4eeb52b225385e8ad2b2f1c4c2ae8f" ns2:_="" ns3:_="" ns4:_="" ns5:_="">
     <xsd:import namespace="b5dd9254-6a80-4550-b647-acdc8f5cf066"/>
@@ -59995,10 +59981,44 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Datum xmlns="b5dd9254-6a80-4550-b647-acdc8f5cf066" xsi:nil="true"/>
+    <TaxCatchAll xmlns="c58b33ff-7e07-4eb2-a566-ce2576b11ca3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1a3513a1-f8f9-433c-9b2a-5ef469d764af">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C8E11B5-DD57-436C-9D2C-B4F470CC558B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D40C02B7-2629-4D1D-998C-3C0981574975}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b5dd9254-6a80-4550-b647-acdc8f5cf066"/>
+    <ds:schemaRef ds:uri="9f573000-1803-4063-935f-650b3da64931"/>
+    <ds:schemaRef ds:uri="1a3513a1-f8f9-433c-9b2a-5ef469d764af"/>
+    <ds:schemaRef ds:uri="c58b33ff-7e07-4eb2-a566-ce2576b11ca3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -60023,22 +60043,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D40C02B7-2629-4D1D-998C-3C0981574975}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C8E11B5-DD57-436C-9D2C-B4F470CC558B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="b5dd9254-6a80-4550-b647-acdc8f5cf066"/>
-    <ds:schemaRef ds:uri="9f573000-1803-4063-935f-650b3da64931"/>
-    <ds:schemaRef ds:uri="1a3513a1-f8f9-433c-9b2a-5ef469d764af"/>
-    <ds:schemaRef ds:uri="c58b33ff-7e07-4eb2-a566-ce2576b11ca3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
